--- a/req3-device/excel/HW01_TestcaseChecklist.xlsx
+++ b/req3-device/excel/HW01_TestcaseChecklist.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC mapping" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -53,7 +53,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +64,21 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,6 +127,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,7 +524,7 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="43.28515625" customWidth="1" min="18" max="18"/>
+    <col width="70" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -640,22 +667,86 @@
           <t>o Accurate - tests what the description says it will test.</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>Objective khớp với các bước và expected ở cả 15 test case.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -666,22 +757,86 @@
           <t>o Economical - has only the steps needed for its purpose</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>Mỗi bước đều phục vụ một expected; bước an toàn ở 02-005 được giữ vì cần thiết.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -692,22 +847,86 @@
           <t>o Repeatable, self standing - same results no matter who tests it.</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="4" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>x: expected dùng từ chủ quan hoặc chưa có ngưỡng ("khoảng 3 giây", "tiếng lạ", "ấm/nóng", "rung mạnh", "không kêu", "cân bằng"); 02-005 chưa rõ cách cấp nguồn; 03-002 còn điều kiện chưa chốt.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -718,22 +937,86 @@
           <t>o Appropriate - for both immediate and future testers</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>x: 02-005 ("công tắc nguồn phù hợp" mơ hồ) và 03-002 (chưa xác nhận quạt có chỉnh nghiêng) khó cho người sau thực hiện đúng.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -744,22 +1027,86 @@
           <t>o Traceable - to a requirement</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="Q8" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>Không có tài liệu yêu cầu của nhà sản xuất; chỉ truy vết được tới chức năng trong sheet Function list.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -770,22 +1117,86 @@
           <t>o Self cleaning - returns the test environment to clean state</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q9" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>x: các test case kết thúc khi quạt còn chạy hoặc còn thay đổi (01-001, 01-002, 01-003, 02-001..02-005, 03-002, 03-004, 04-001); chưa có bước tắt quạt/khôi phục. 03-002 còn để nguyên góc nghiêng.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -820,22 +1231,86 @@
           <t>o Has a name and number</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Tất cả có ID theo dạng NN - 00M và tên.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -846,22 +1321,86 @@
           <t>o Has a stated purpose that includes what requirement is being tested</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>Objective nêu mục đích; chưa có tài liệu yêu cầu để tham chiếu (xem mục 5).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -872,22 +1411,86 @@
           <t>o Has a description of the method of testing</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>Các bước mô tả phương pháp test bằng thao tác cụ thể.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -898,22 +1501,86 @@
           <t>o Specifies setup information - environment, data, prerequisite tests, security access</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-      <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q14" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>x: 01-005, 02-005, 04-001 chưa tách Precondition riêng (nằm trong bước hoặc ghi chú an toàn).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -924,22 +1591,86 @@
           <t>o Has actions and expected results</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="4" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>Có bước và expected cho mọi test case.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -950,22 +1681,86 @@
           <t>o States if any proofs, such as reports or screen grabs, need to be saved</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>o: đã có video hoặc yêu cầu ghi số đo. x: chưa nêu bằng chứng cần lưu (video, ảnh, số đo).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -976,22 +1771,86 @@
           <t>o Leaves the testing environment clean</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
-      <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q17" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>Giống mục 6: chưa có bước trả quạt về trạng thái tắt/ban đầu ở các test case đang chạy.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1002,22 +1861,86 @@
           <t>o Uses active case language</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>Các bước dùng câu mệnh lệnh (Nhấn, Quan sát, Ghi lại...).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1028,22 +1951,86 @@
           <t>o Does not exceed 15 steps</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="n"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q19" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>Không test case nào quá 6 bước.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1054,22 +2041,86 @@
           <t>o Matrix does not take longer than 20 minutes to test</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n"/>
-      <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="n"/>
-      <c r="R20" s="4" t="n"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>x: 02-001 chạy 30 phút, vượt 20 phút.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1080,22 +2131,86 @@
           <t>o Automated script is commented with purpose, inputs, expected results</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="4" t="n"/>
-      <c r="P21" s="4" t="n"/>
-      <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="4" t="n"/>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>Không có script tự động.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1106,22 +2221,86 @@
           <t>o Setup offers alternative to prerequisite tests, if possible</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="P22" s="4" t="n"/>
-      <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="4" t="n"/>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>o: precondition nêu trạng thái cần có, không phụ thuộc test case khác.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1132,22 +2311,86 @@
           <t>o Is in correct business scenario order with other tests</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n"/>
-      <c r="P23" s="4" t="n"/>
-      <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="4" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q23" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>Thứ tự ID theo luồng: bật → đổi tốc độ → tắt → vận hành → an toàn → đảo gió.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -1182,22 +2425,86 @@
           <t>o Employs naming and numbering conventions</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
-      <c r="O25" s="4" t="n"/>
-      <c r="P25" s="4" t="n"/>
-      <c r="Q25" s="4" t="n"/>
-      <c r="R25" s="4" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q25" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>Quy ước ID thống nhất theo mẫu template.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1208,22 +2515,86 @@
           <t>o Saved in specified formats, file types</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
-      <c r="O26" s="4" t="n"/>
-      <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="n"/>
-      <c r="R26" s="4" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="Q26" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="inlineStr">
+        <is>
+          <t>Lưu ở .xlsx theo template và .md.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1234,22 +2605,86 @@
           <t>o Is versioned to match software under test</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
-      <c r="O27" s="4" t="n"/>
-      <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="4" t="n"/>
-      <c r="R27" s="4" t="n"/>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="P27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="Q27" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="R27" s="10" t="inlineStr">
+        <is>
+          <t>Thiết bị vật lý không có phiên bản phần mềm; model ghi trong device.md.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1260,22 +2695,86 @@
           <t>o Includes test objects needed by the case, such as databases</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
-      <c r="O28" s="4" t="n"/>
-      <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="4" t="n"/>
-      <c r="R28" s="4" t="n"/>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="P28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="Q28" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="R28" s="10" t="inlineStr">
+        <is>
+          <t>o: 02-003 nêu ứng dụng đo ồn, 02-004 nêu dải ruy băng. x: 02-005 chưa xác định đối tượng cấp nguồn (ổ cắm có công tắc?).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1286,22 +2785,86 @@
           <t>o Stored as read</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
-      <c r="O29" s="4" t="n"/>
-      <c r="P29" s="4" t="n"/>
-      <c r="Q29" s="4" t="n"/>
-      <c r="R29" s="4" t="n"/>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="P29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="Q29" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="inlineStr">
+        <is>
+          <t>Bài tập lưu trên Git cá nhân, không áp dụng.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1312,22 +2875,86 @@
           <t>o Stored with controlled access</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="4" t="n"/>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="M30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="P30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="Q30" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="R30" s="10" t="inlineStr">
+        <is>
+          <t>Bài tập lưu trên Git cá nhân, không áp dụng.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -1338,22 +2965,86 @@
           <t>o Stored where network backup operates</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
-      <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n"/>
-      <c r="R31" s="4" t="n"/>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="P31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="Q31" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="inlineStr">
+        <is>
+          <t>Bài tập lưu trên Git cá nhân, không áp dụng.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -1364,22 +3055,86 @@
           <t>o Archived off-site</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-      <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n"/>
-      <c r="R32" s="4" t="n"/>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="K32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="M32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="P32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="Q32" s="12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="inlineStr">
+        <is>
+          <t>Bài tập lưu trên Git cá nhân, không áp dụng.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1393,9 +3148,285 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID test case</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Test case name (Objective)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TC1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01-001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bật quạt ở tốc độ 1 bằng nút bấm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01-002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chuyển tốc độ tăng dần 1 → 2 → 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01-003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chuyển tốc độ giảm dần 3 → 2 → 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TC4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01-004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tắt quạt bằng nút Off khi đang chạy tốc độ 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01-005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nhấn đồng thời hai nút tốc độ 1 và 2 khi quạt không có điện</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>02-001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chạy liên tục 30 phút ở tốc độ 3 (nhiệt độ và độ bền)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>02-002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Độ ổn định của đế khi chạy tốc độ 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>02-003</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Độ ồn theo từng mức tốc độ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>02-004</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lưu lượng và hướng gió theo tốc độ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>02-005</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cấp điện khi nút tốc độ 1 đã được chọn trong lúc quạt không có điện</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>03-001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lồng bảo vệ chắc chắn và khe hở an toàn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>03-002</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Điều chỉnh góc nghiêng đầu quạt (chỉ thực hiện nếu quạt có chỉnh nghiêng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>03-003</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kiểm tra dây điện và phích cắm</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>03-004</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cánh quạt cân bằng và không chạm lồng</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>04-001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ngừng đảo gió khi quạt đang chạy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
